--- a/data/consommation.xlsx
+++ b/data/consommation.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="consommation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Méthodologie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,12 +29,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -40,8 +55,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
+        <fgColor rgb="00305496"/>
+        <bgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,11 +90,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,14 +467,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>code_matiere</t>
@@ -442,58 +486,2672 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>designation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>conso_moyenne_jour</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nb_commandes_utilisees</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>methode</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>confiance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MP001</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>45</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR4.0</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR4.0 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MP002</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>20</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR5.0</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR5.0 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MP025</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR5.5</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR5.5 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MP050</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR6.0</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR6.0 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MP010</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR7.0</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR7.0 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-FO3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 150x90x15 | FO3 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-FO4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x15 | FO4 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-PR10</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x20 | PR10 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-PR12</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x20 | PR12 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-PR14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 150x90x20 | PR14 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-PR5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 150x90x15 | PR5 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-PR6</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 150x90x15 | PR6 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-PR8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 150x90x15 | PR8 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RO1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x15 | RO1 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RO2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x15 | RO2 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RO3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 150x90x15 | RO3 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RO5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x15 | RO5 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RO6</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x20 | RO6 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RO7</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x20 | RO7 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RT1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x15 | RT1 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RT3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x15 | RT3 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RT5</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x15 | RT5 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RT6</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x20 | RT6 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CP3GL-RT7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRENELAGES | 125x82x20 | RT7 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CPBSM</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BROSSE SPIRALE METALLIQUE | 60x1000</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CPBSP</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>BROSSE SPIRALE PLASTIQUE | 57x1000mm | 0.6mm</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CPEDT</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>EAU DISTILLEE TECHNIQUE | 0-2µS/cm</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>58.824</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CPHDC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>HUILE DE COUPE SOLUBLE DANS L'EAU</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CPHDP</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HUILE DE PROTECTION | PROTECT150</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>74.336</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CPJEX</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>JEX</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CPLUB</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>LUBRIFIANT | AT115</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CPMGE</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>MOYEUX PORTE GALETS DE CRENELAGE | 82x15mm | 25mm</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CPPDM</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>PIERE DE MEULE | 100x20x16</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>FOU-EXPL</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>FOURNITURES POUR EXPLOITATION | PC | CHECKLISTC</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>FOU-EXPL-50FEUILLES</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>FOURNITURES POUR EXPLOITATION | 50FEUILLES | FICHRECEFM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>OTAPIU001</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PINCE UNIVERSELLE | 200mm | FCM187.20G</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>OTATER001</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>TENAILLE RUSSE | 200mm</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>PCHCL37%</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ACIDE CHLORHYDRIQUE HCL 37%</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>PCMET</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>METHANOL | M=32.04 | CH3OH</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>PEAMF</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ANNEAU POUR MANUTENTION FUT | 75x60</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>54.545</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>PEBET-JAUNE-1018</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>BOBINE EN TOLE | 255x118x33 | JAUNE-1018 | B60</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>PECAC-KRAFT-KRAF</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CAISSE EN CARTON | 35x16.5x35 | KRAFT-KRAF | SIMPLE</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>PECAG</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CACHET GALVANISE | 56x0.90</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>PECBP-T-CHIMIQUE</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CALE EN BOIS PC STRAND | 75x75x750 | T-CHIMIQUE | CARRE</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>PECEB</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CALE EN BOIS | 600 | TRIANG</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>PECEC-KRAFT-KRAF</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>CERSEAU EN CARTON | 690x360 | KRAFT-KRAF | SIMPLE</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>PECOR</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>CORDE | 12</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>PECTA-NOIR</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>CAPUCHON THERMORETRACTABLE ENDUIT D'ADHESIF (PROTECTION PCS) | 22x55mm | NOIR | CAPUCHON</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>PEETA-JAUNE</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ETIQUETTE AUTOCOLLANTE | 100x200 | JAUNE</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>3.436</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>PEETG</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ETIQUETTE GRAPHIPLAST | 105x147.63</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>PEFCP</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>FILM DE COUVERTURE POUR PICK-UP | 120µ | 100cm</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>PEFEC</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>FUT EN CARTON | 357x280x10</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>21.407</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>PEFEM</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>FEUILLARD METTALIQUE | 19x0.90</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>PEFEP-BLANC-LAIT</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE ETIRABLE (MEDIA POWER MACHNE) | 50 | BLANC-LAIT</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>PEFEP-BLEU</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE ETIRABLE (MEDIA POWER MACHNE) | 50 | BLEU</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>PEFEP-JAUNE</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE ETIRABLE (MEDIA POWER MACHNE) | 50 | JAUNE</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>PEFEP-MARRON</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE ETIRABLE (MEDIA POWER MACHNE) | 50 | MARRON</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>PEFEP-TRANSPAR</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE ETIRABLE (MEDIA POWER MACHNE) | 80 | TRANSPAR</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>PEFEP-VERT</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE ETIRABLE (MEDIA POWER MACHNE) | 50 | VERT</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>13.138</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>PEFPE-TRANSPAR</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE ETIRABLE MANUEL | 50 | TRANSPAR | 30</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>385.013</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>PEFPL</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>FEUILLARD PLASTIQUE | 15x0.8mm</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>PEFPP-TRANSPAR</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>FILM EN PLASTIQUE THERMO RETRACTABLE POUR PC STRAND | 120 | TRANSPAR | 100</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>PEHPR-CRISTAL</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>HOUSSE EN PLASTIQUE RETRACTABLE PEBD | 1.25x2.85 | CRISTAL | 170</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>PEP10</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>POINTE N° 10</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>PEPAC-KNIT-CREPE</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>PAPIER CREPE | 120x76x360 | KNIT-CREPE | AVEC-VCI</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>PEPEB</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>PALETTE EN BOIS | 105x105mm | NEUVE</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>2.788</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>PEPEC-20</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>PLAQUE EN CARTON SIMPLE ONDULATION | 750x750mm | 20 | KRAFT/KRAF</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>8.590999999999999</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>PERPR-BLEU</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>ROULEAU EN PLASTIQUE RETRACTABLE PEBD | 1.25+15+15 | BLEU | 170µ</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>PERPR-CRISTA</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ROULEAU EN PLASTIQUE RETRACTABLE PEBD | 1.25+15+15 | CRISTA | 170µ</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>PERPR-JAUNE</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ROULEAU EN PLASTIQUE RETRACTABLE PEBD | 1.25+15+15 | JAUNE | 170µ</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>PERPR-TRANSPARAN</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ROULEAU EN PLASTIQUE RETRACTABLE PEBD | 1.25+15+15 | TRANSPARAN | 170µ</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>PERPR-VERT</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ROULEAU EN PLASTIQUE RETRACTABLE PEBD | 1.25+15+15 | VERT | 170µ</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>PESCO-ROUGE</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SCOTCH | 48x100 | ROUGE</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>PESCO-TRANSPAR</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SCOTCH | 48x100 | TRANSPAR</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>PESEP-NOIR</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SACHET EN PLASTIQUE POUR PICK-UP | 60x80cm | NOIR | SACHET</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>491.803</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>PESMP-NOIR</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>STYLO MARQUEUR PERMENAT | 5mm | NOIR | GM</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>PESPI-BLANC-MAK</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SCOTCH PP IMPRIME 2 COULEURS | 73.5x100 | BLANC-MAK | ROUGE-NOIR</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>PETJT-MARRON</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ROULEAU EN TOILE DE JUTTE TISSE | MARRON</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>PETPT-BLANC</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>TOILE EN POLYPROPYLENE TISSE | 15cm | BLANC | 60 g/m²</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>PGCIR</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>CIRE | 3104W</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>PGFLF</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>FLOR FLUX | ZnCI22NH4C</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>PGPLO</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>PLOMB | 99.94%MIN</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>PGTER</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>TAMPON D'ESSUYAGE EN ROULEAU | 25x25mm</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>TSARB</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ACCELERATEUR DE REACTION DE BAIN DE PHOSPHATE | BONDERITE</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TSBOR</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>BORAX | BONDERITE</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>TSCDS</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>CARBONATE DE SOUDE</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TSIDA</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>INHIBITEUR D'ATTAQUE D'ACIDE | CADD4HENKE</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>TSIDF</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>INHIBITEUR DE FUMEE | CLEAN-E200</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>aucun historique de commande trouvé pour cet article</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>aucune_donnee</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>TSPDZ</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>PHOSPHATE DE ZINC | M-ZN4804RX | BONDERITE</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
         <v>150</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>historique_materiau</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ZINCE</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ZINC ELECTROLYTIQUE | 99.995%MIN | SHG</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>periode_globale_1_commande</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>faible_1_commande</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="115" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Comment conso_moyenne_jour a été calculée</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Source : historique_fournisseurs.xlsx (162 commandes réelles, du 22/11/2024 au 27/06/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Chaque désignation de commande a été rapprochée du bon code_matiere réel (matching par similarité de texte).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Seules les correspondances avec un score de similarité &gt;= 0.65 ont été retenues (72/162 lignes) ; les autres</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>commandes concernent des articles hors périmètre matières (fournitures administratives, outillage...) ou</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>des désignations trop différentes pour être rapprochées de façon fiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Formule : conso_moyenne_jour = quantité totale commandée / nombre de jours observés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Si un article a 2 commandes ou plus : jours observés = écart entre la 1ère et la dernière réception de CET article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Si un article n'a qu'1 seule commande : jours observés = période totale du fichier (582 jours), par défaut faute de mieux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Confiance :</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  haute = au moins 3 commandes historiques observées pour cet article</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  moyenne = 2 commandes historiques observées</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  faible_1_commande = une seule commande observée sur toute la période (estimation à prendre avec précaution)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  aucune_donnee = aucune commande de cet article trouvée dans l'historique fournisseur (22/90 matières couvertes, 68 sans donnée)</t>
+        </is>
       </c>
     </row>
   </sheetData>
